--- a/prix/cecil-fongicide.xlsx
+++ b/prix/cecil-fongicide.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\caisse5\Desktop\site-internet\peintures\prix\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\peintures\prix\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9065A83D-BC6C-4D21-833B-BA992C7EAF24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4786874-C34D-4FAA-9B70-85E3ABAAFB96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="24612" yWindow="120" windowWidth="13236" windowHeight="9708" xr2:uid="{6E95DC93-531D-460D-9A06-44397A8920D7}"/>
+    <workbookView xWindow="22932" yWindow="-108" windowWidth="19416" windowHeight="11016" xr2:uid="{6E95DC93-531D-460D-9A06-44397A8920D7}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -573,7 +573,7 @@
         <v>10</v>
       </c>
       <c r="F3" s="11">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">

--- a/prix/cecil-fongicide.xlsx
+++ b/prix/cecil-fongicide.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\peintures\prix\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\caisse5\Desktop\pages-GitHub Braconnier\peintures\prix\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4786874-C34D-4FAA-9B70-85E3ABAAFB96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10A0BA03-E53C-4E61-815E-2DE037048E48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22932" yWindow="-108" windowWidth="19416" windowHeight="11016" xr2:uid="{6E95DC93-531D-460D-9A06-44397A8920D7}"/>
+    <workbookView xWindow="23520" yWindow="0" windowWidth="19116" windowHeight="10884" xr2:uid="{6E95DC93-531D-460D-9A06-44397A8920D7}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -553,7 +553,7 @@
         <v>9</v>
       </c>
       <c r="F2" s="11">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
@@ -573,7 +573,7 @@
         <v>10</v>
       </c>
       <c r="F3" s="11">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">

--- a/prix/cecil-fongicide.xlsx
+++ b/prix/cecil-fongicide.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\caisse5\Desktop\pages-GitHub Braconnier\peintures\prix\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\peintures\prix\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10A0BA03-E53C-4E61-815E-2DE037048E48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAC78B5E-B1BB-4C21-B28C-49FBF07939F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="23520" yWindow="0" windowWidth="19116" windowHeight="10884" xr2:uid="{6E95DC93-531D-460D-9A06-44397A8920D7}"/>
+    <workbookView xWindow="22932" yWindow="-108" windowWidth="19416" windowHeight="11016" xr2:uid="{6E95DC93-531D-460D-9A06-44397A8920D7}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -567,13 +567,13 @@
         <v>13</v>
       </c>
       <c r="D3" s="10">
-        <v>63.190000000000005</v>
+        <v>63.2</v>
       </c>
       <c r="E3" s="9" t="s">
         <v>10</v>
       </c>
       <c r="F3" s="11">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
